--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,13 +454,13 @@
           <t>Apple Cider (Gal)</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>4</v>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -474,9 +474,7 @@
       <c r="C3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
         <v>1</v>
@@ -488,11 +486,11 @@
           <t>Bag Paper - Baguette</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -508,34 +506,42 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Box Cake - 10x10x5</t>
+          <t>Capers</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Box Cake - 6x6x3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
       <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
@@ -543,207 +549,217 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Box Cake - 8x8x2.5</t>
+          <t>Chobani - Drinkable Yogurt (Protein Strawberry)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Box Cake - 8x8x5</t>
+          <t>Chobani - Drinkable Yogurt (protein mixed berry)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Capers</t>
+          <t>Chobani - Drinkables (Assorted Case)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2</v>
-      </c>
+          <t>Coffee Stirrer (Bamboo)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Chobani - Drinkable Yogurt (asst case)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coffee Stirrer (Bamboo)</t>
+          <t>Container - Deli (8oz)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Container - Deli (16oz)</t>
+          <t>Container - Plastic Clamshell (6")</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>3</v>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Container - Deli (32oz)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
+          <t>Container - Soup (16oz)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Container - Muffin (1 Pack)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Container - Soup (32oz)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Container - Plastic Clamshell (6")</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>Container - Soup (8oz)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Container - Soup (16oz)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
+          <t>Cup - Espresso (4oz)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Container - Soup (32oz)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>Cup - Hot (8oz)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Container - Soup (8oz)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Cup - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cup - Espresso (4oz)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
@@ -751,40 +767,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cup - Hot (8oz)</t>
+          <t>Employee Water</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
       <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
         <v>4</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cup - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>Essentia Water</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cup - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
+          <t>Evian 1L</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>1</v>
@@ -795,47 +815,45 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Employee Water</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
-      </c>
+          <t>FRZ Fruit - Mango</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>5</v>
-      </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
+          <t>Fiji Water 1L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
@@ -843,7 +861,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Mango</t>
+          <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -851,15 +869,15 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
+          <t>Grandma's Coffee Cake - Banana Walnut</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -867,57 +885,55 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
+          <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fiji Water 500ml</t>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flax Seeds</t>
+          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Floor Cleaner - Lucky 7</t>
+          <t>Grandma's Coffee Cake - Cranberry</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -926,70 +942,80 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
+          <t>Hazelnut Coffee (Grounded, Bulk)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
+          <t>Honey - Jug</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon w/ Nuts</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>Hot Chocolate (Bulk)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cranberry</t>
+          <t>Ithaca Soda - Ginger Beer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Mixed Berry</t>
+          <t>Java Box (160oz)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1003,29 +1029,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Hazelnut Coffee (Grounded, Bulk)</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
-        <v>1</v>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Honey - Jug</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
+          <t>Joe Tea - Black Cherry</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1033,149 +1057,147 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jacquet - Belgian Waffles</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>Kilogram Chai Concentrate</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>3</v>
+      </c>
       <c r="C41" t="n">
         <v>1</v>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Java Box (160oz)</t>
+          <t>Lid - Deli (6/32oz)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>Lid - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Joe Tea - Black Cherry</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Kilogram Chai Concentrate</t>
+          <t>Lid - Soup (32oz)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="n">
-        <v>2</v>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>3</v>
-      </c>
-      <c r="F45" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lid - Deli (6/32oz)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>Lid - Soup (6/16 oz)</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
       <c r="C46" t="n">
         <v>1</v>
       </c>
-      <c r="D46" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
       <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lid - Hot Cup (8oz)</t>
+          <t>Maple Syrup (pure)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lid - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
+          <t>Matcha - Jade Leaf</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lid - Portion (3.25oz)</t>
+          <t>Monin - Butter Pecan</t>
         </is>
       </c>
       <c r="B49" t="n">
         <v>1</v>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lid - Soup (32oz)</t>
+          <t>Mop Head Cut (White)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
@@ -1185,18 +1207,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>8</v>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
+          <t>Oil - Olive Extra Virgin</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="n">
         <v>1</v>
       </c>
@@ -1205,65 +1221,55 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lid Espresso - 4oz</t>
+          <t>Peanut Butter - Chunky</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Maple Syrup (pure)</t>
+          <t>Peanut Butter - Creamy</t>
         </is>
       </c>
       <c r="B53" t="n">
         <v>1</v>
       </c>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Matcha - Jade Leaf</t>
+          <t>Plate - Paper (7")</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" t="n">
-        <v>2</v>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Monin - Butter Pecan</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
@@ -1271,7 +1277,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mop Head Cut (White)</t>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1279,50 +1285,48 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Panini Sheets - 16x8 3/8</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>2</v>
-      </c>
+          <t>Saratoga Sparkling 12oz</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
+          <t>Saratoga Sparkling 28oz</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Plate - Paper (7")</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
+          <t>Scrubbies - Steel</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
         <v>1</v>
       </c>
@@ -1333,41 +1337,43 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Red Bull - Amber</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+          <t>Smoked Salmon (Sliced)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Red Bull - Yellow</t>
+          <t>Supplement - Antioxident</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
@@ -1377,272 +1383,274 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
+          <t>Supplement - Collagen</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 12oz</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
       <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 28oz</t>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>6</v>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>3</v>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
-      <c r="D67" t="n">
-        <v>3</v>
-      </c>
+          <t>Tea Bags - Irish Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Supplement - Whey Protein</t>
+          <t>Tea Bags - Lemon Ginger (Twinings)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sweet Street - Chocolate Lovin</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - Pomegrantate &amp; Rasp (Twinings)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tea Bags - Decaf English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>5</v>
+      </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>6</v>
-      </c>
+          <t>Tissues/Kleenex</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="n">
         <v>3</v>
       </c>
-      <c r="D71" t="n">
-        <v>4</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>6</v>
-      </c>
-      <c r="C72" t="n">
-        <v>3</v>
-      </c>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
       <c r="C73" t="n">
-        <v>1</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tea Bags - Pomegrantate &amp; Rasp (Twinings)</t>
+          <t>Torani - White Chocolate Sauce</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
-      </c>
-      <c r="C74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="n">
+        <v>2</v>
+      </c>
       <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>3</v>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="n">
-        <v>2</v>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tissues/Kleenex</t>
+          <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="n">
-        <v>6</v>
-      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Vita Coco - Pineapple</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="n">
-        <v>1</v>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>3</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Wrap - Foil (9" x 10.75")</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>7</v>
-      </c>
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>4</v>
-      </c>
-      <c r="E78" t="n">
-        <v>4</v>
-      </c>
-      <c r="F78" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
+          <t>Wrap - Paper (15" x 10.75")</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
         <v>1</v>
@@ -1651,138 +1659,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>Wrap - Paper (6" x 10.75")</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
-      </c>
-      <c r="C80" t="n">
-        <v>1</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="n">
-        <v>2</v>
-      </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Urnex - Cafiza</t>
+          <t>Yancey's - Fancy XXX'tra Sharp Stick</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Urnex - Rinza</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Vita Coco - Coconut Water 1L</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1</v>
-      </c>
-      <c r="F84" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>2</v>
-      </c>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>3</v>
-      </c>
-      <c r="C86" t="n">
-        <v>1</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Wrap - Paper (6" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,13 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apple Cider (Gal)</t>
+          <t>Acai Powder</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>1</v>
       </c>
@@ -467,44 +465,44 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bag - Wax (Sandwich)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Apple Cider (Gal)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bag Paper - Baguette</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+          <t>Bag - Poly (Retail Portion)</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bindi - Cake Tiramisu Round</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
+          <t>Bag - Wax (Sandwich)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>1</v>
@@ -513,35 +511,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Capers</t>
+          <t>Bag Paper - Baguette</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
+          <t>Bindi - Cake Tiramisu Round</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>1</v>
       </c>
@@ -549,37 +539,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chobani - Drinkable Yogurt (Protein Strawberry)</t>
+          <t>Capers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Chobani - Drinkable Yogurt (protein mixed berry)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -588,13 +578,13 @@
           <t>Chobani - Drinkables (Assorted Case)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -603,116 +593,122 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Container - Deli (32oz)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>Container - Deli (16oz)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Container - Deli (8oz)</t>
+          <t>Container - Deli (32oz)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Container - Plastic Clamshell (6")</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
+          <t>Container - Deli (8oz)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Container - Soup (16oz)</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>6</v>
-      </c>
+          <t>Container - Muffin (1 Pack)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
         <v>1</v>
       </c>
-      <c r="D15" t="n">
-        <v>3</v>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Container - Soup (32oz)</t>
+          <t>Container - Plastic Clamshell (6")</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Container - Soup (8oz)</t>
+          <t>Container - Soup (16oz)</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
       <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cup - Espresso (4oz)</t>
+          <t>Container - Soup (32oz)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
         <v>1</v>
@@ -721,43 +717,49 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cup - Hot (8oz)</t>
+          <t>Container - Soup (8oz)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
       <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cup - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>Cup - Espresso (4oz)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
       <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Degreaser - for Panini Press (Dawn)</t>
+          <t>Cup - Hot (8oz)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
@@ -767,31 +769,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Employee Water</t>
+          <t>Cup - Portion (3.25oz)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
-        <v>4</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>1</v>
       </c>
@@ -801,111 +799,113 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>Egg Patty - Vegan</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Mango</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+          <t>Employee Water</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>4</v>
+      </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
+          <t>Essentia Water</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
+          <t>Evian 1L</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="n">
-        <v>3</v>
-      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Apple</t>
+          <t>FRZ Fruit - Mango</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>1</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Banana Walnut</t>
+          <t>Fiji Water 1L</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
       <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Flax Seeds</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+          <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -919,21 +919,21 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
+          <t>Grandma's Coffee Cake - Blueberry</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cranberry</t>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -942,80 +942,72 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Hazelnut Coffee (Grounded, Bulk)</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2</v>
-      </c>
+          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Honey - Jug</t>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" t="n">
-        <v>4</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Hot Chocolate (Bulk)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2</v>
-      </c>
+          <t>Grandma's Coffee Cake - Mixed Berry</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Ginger Beer</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>Hazelnut Coffee (Grounded, Bulk)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
       <c r="C37" t="n">
         <v>1</v>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Java Box (160oz)</t>
+          <t>Honey - Jug</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1029,69 +1021,65 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
+          <t>Iced Tea - Black</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Joe Tea - Black Cherry</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
+          <t>Iced Tea - Green Citrus Ginko</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kilogram Chai Concentrate</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3</v>
-      </c>
-      <c r="C41" t="n">
-        <v>1</v>
-      </c>
+          <t>Ithaca Soda - Ginger Beer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>2</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lid - Deli (6/32oz)</t>
+          <t>Ithaca Soda - Root Beer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lid - Portion (2oz)</t>
+          <t>Jam - Strawberry (Retail)</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1105,44 +1093,42 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lid - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
+          <t>Java Box (160oz)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lid - Soup (32oz)</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>2</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+          <t>Joe Tea - Black Cherry</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>1</v>
+      </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
@@ -1151,24 +1137,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Maple Syrup (pure)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+          <t>Kilogram Chai Concentrate</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2</v>
+      </c>
       <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Matcha - Jade Leaf</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>Lid - Deli (6/32oz)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
@@ -1179,143 +1175,155 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Monin - Butter Pecan</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mop Head Cut (White)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2</v>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+          <t>Lid - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2</v>
+      </c>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oil - Olive Extra Virgin</t>
+          <t>Lid - Soup (32oz)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Peanut Butter - Chunky</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
+          <t>Lid - Soup (6/16 oz)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
       <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
       <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid Espresso - 4oz</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
       <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Plate - Paper (7")</t>
+          <t>Maple Syrup (pure)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
       <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Red Bull</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>Matcha - Jade Leaf</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
       <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
+          <t>Monin - Butter Pecan</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 12oz</t>
+          <t>Monin - Cinnamon</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 28oz</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Mop Head Cut (White)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
@@ -1323,58 +1331,62 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Scrubbies - Steel</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>Peanut Butter - Creamy</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>2</v>
+      </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>Plate - Paper (7")</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="n">
-        <v>1</v>
-      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" t="n">
-        <v>2</v>
-      </c>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Supplement - Antioxident</t>
+          <t>Red Bull - Amber</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>1</v>
@@ -1383,155 +1395,147 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Supplement - Collagen</t>
+          <t>Register Tape - Paper (3" x 165')</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="n">
-        <v>2</v>
-      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" t="n">
-        <v>2</v>
-      </c>
-      <c r="D64" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>2</v>
-      </c>
-      <c r="F64" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>6</v>
-      </c>
+          <t>Saratoga Sparkling 12oz</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>6</v>
-      </c>
-      <c r="E65" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
+          <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tea Bags - Irish Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+          <t>Smoked Salmon (Sliced)</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="n">
-        <v>6</v>
-      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Tea Bags - Lemon Ginger (Twinings)</t>
+          <t>Supplement - Antioxident</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="n">
-        <v>6</v>
-      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Tea Bags - Pomegrantate &amp; Rasp (Twinings)</t>
+          <t>Supplement - Collagen</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>5</v>
-      </c>
+          <t>Supplement - Whey Protein</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
       <c r="E70" t="n">
-        <v>2</v>
-      </c>
-      <c r="F70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tissues/Kleenex</t>
+          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Sweet Street - Pie Caramel Apple Granny Sliced</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1539,119 +1543,121 @@
       <c r="D72" t="n">
         <v>1</v>
       </c>
-      <c r="E72" t="n">
-        <v>4</v>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
-      </c>
-      <c r="C73" t="n">
-        <v>3</v>
-      </c>
-      <c r="D73" t="n">
-        <v>4</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="n">
-        <v>2</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Urnex - Rinza</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>8</v>
+      </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
       <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Vita Coco - Pineapple</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>6</v>
+      </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="n">
+        <v>2</v>
+      </c>
       <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
+          <t>Tissues/Kleenex</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="n">
-        <v>1</v>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2</v>
+      </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
@@ -1659,30 +1665,198 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Wrap - Paper (6" x 10.75")</t>
+          <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Yancey's - Fancy XXX'tra Sharp Stick</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="n">
-        <v>2</v>
-      </c>
+          <t>Torani - Pumpkin Pie Sauce</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Urnex - Cafiza</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Vita Coco - Coconut Water 1L</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Vita Coco - Coconut Water 500ml</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Wrap - EZ Poly (8" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Wrap - Foil (9" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>2</v>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (6" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,9 @@
         <v>1</v>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -808,44 +810,46 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Employee Water</t>
+          <t>Eggs (In-Shell)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
-        <v>4</v>
-      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
+          <t>Employee Water</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4</v>
+      </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
+          <t>Essentia Water</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -859,109 +863,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Mango</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
+          <t>Evian 1L</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>2</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>FRZ Fruit - Mango</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Flax Seeds</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
+          <t>Fiji Water 1L</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
       <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Apple</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>Flax Seeds</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
+          <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Chip</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
+          <t>Grandma's Coffee Cake - Blueberry</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
+          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -975,31 +979,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Mixed Berry</t>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hazelnut Coffee (Grounded, Bulk)</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>2</v>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
+          <t>Grandma's Coffee Cake - Mixed Berry</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1007,13 +1007,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Honey - Jug</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>Hazelnut Coffee (Grounded, Bulk)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
@@ -1021,27 +1025,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Iced Tea - Black</t>
+          <t>Honey - Jug</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Iced Tea - Green Citrus Ginko</t>
+          <t>Ice Melt</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
@@ -1049,27 +1053,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Ginger Beer</t>
+          <t>Iced Tea - Black</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
       <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Root Beer</t>
+          <t>Ithaca Soda - Ginger Beer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>1</v>
       </c>
@@ -1079,208 +1081,202 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jam - Strawberry (Retail)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+          <t>Ithaca Soda - Root Beer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Box (160oz)</t>
+          <t>Jacquet - Belgian Waffles</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>Jam - Strawberry (Retail)</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Joe Tea - Black Cherry</t>
+          <t>Java Box (160oz)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Kilogram Chai Concentrate</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2</v>
-      </c>
-      <c r="E47" t="n">
-        <v>6</v>
-      </c>
+          <t>Java Box (96oz)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Lid - Deli (6/32oz)</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>2</v>
-      </c>
+          <t>Joe Tea - Black Cherry</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lid - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+          <t>Kilogram Chai Concentrate</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
       <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lid - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>Lid - Deli (6/32oz)</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lid - Soup (32oz)</t>
+          <t>Lid - Portion (2oz)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>3</v>
-      </c>
+          <t>Lid - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lid Espresso - 4oz</t>
+          <t>Lid - Soup (32oz)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Maple Syrup (pure)</t>
+          <t>Lid - Soup (6/16 oz)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Matcha - Jade Leaf</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>3</v>
-      </c>
+          <t>Lid Espresso - 4oz</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="n">
         <v>1</v>
       </c>
@@ -1289,26 +1285,34 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Monin - Butter Pecan</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>Maple Syrup (pure)</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="n">
+        <v>2</v>
+      </c>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Monin - Cinnamon</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>Matcha - Jade Leaf</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3</v>
+      </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
@@ -1317,45 +1321,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Mop Head Cut (White)</t>
+          <t>Monin - Butter Pecan</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
+          <t>Monin - Cinnamon</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
       <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Plate - Paper (7")</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Mop Head Cut (White)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
@@ -1363,7 +1363,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Mustard - Honey</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -1371,22 +1371,18 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Red Bull - Amber</t>
+          <t>Oats</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="n">
-        <v>1</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="n">
         <v>1</v>
@@ -1395,21 +1391,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Register Tape - Paper (3" x 165')</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Peanut Butter - Creamy</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2</v>
+      </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
+          <t>Plate - Paper (7")</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1417,66 +1417,64 @@
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 12oz</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
+          <t>Red Bull - Amber</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
       <c r="D66" t="n">
         <v>1</v>
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>5</v>
-      </c>
+          <t>Register Tape - Paper (3" x 165')</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>1</v>
       </c>
-      <c r="D67" t="n">
-        <v>3</v>
-      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Supplement - Antioxident</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
@@ -1487,21 +1485,21 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Supplement - Collagen</t>
+          <t>Saratoga Sparkling 12oz</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Supplement - Whey Protein</t>
+          <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -1509,227 +1507,209 @@
       <c r="D70" t="n">
         <v>1</v>
       </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr"/>
+          <t>Smoked Salmon (Sliced)</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>5</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="inlineStr"/>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sweet Street - Pie Caramel Apple Granny Sliced</t>
+          <t>Sugar - Extra Fine</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
+          <t>Sugar - Light Brown</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>6</v>
-      </c>
-      <c r="C74" t="n">
-        <v>3</v>
-      </c>
+          <t>Supplement - Antioxident</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="n">
-        <v>6</v>
-      </c>
+      <c r="E74" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>8</v>
-      </c>
-      <c r="C75" t="n">
-        <v>3</v>
-      </c>
+          <t>Supplement - Collagen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="n">
-        <v>6</v>
-      </c>
+      <c r="E75" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
+          <t>Supplement - Whey Protein</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>6</v>
-      </c>
+          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="n">
-        <v>2</v>
-      </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Tissues/Kleenex</t>
+          <t>Sweet Street - Pie Caramel Apple Granny Sliced</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="n">
-        <v>2</v>
-      </c>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
+          <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
         </is>
       </c>
       <c r="B79" t="n">
         <v>1</v>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" t="n">
-        <v>2</v>
-      </c>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C80" t="n">
         <v>3</v>
       </c>
-      <c r="D80" t="n">
-        <v>4</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2</v>
-      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>1</v>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="n">
-        <v>2</v>
-      </c>
-      <c r="F82" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Urnex - Cafiza</t>
+          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="n">
         <v>2</v>
@@ -1739,46 +1719,54 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Urnex - Rinza</t>
+          <t>Tissues/Kleenex</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="n">
-        <v>2</v>
-      </c>
-      <c r="F84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 1L</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>2</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3</v>
+      </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
@@ -1787,74 +1775,174 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Wrap - EZ Poly (8" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="n">
-        <v>1</v>
-      </c>
+          <t>Torani - Pumpkin Pie Sauce</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="n">
-        <v>3</v>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
+          <t>Torani - White Chocolate Sauce</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
       </c>
-      <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
+          <t>Urnex - Cafiza</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
-      <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="n">
-        <v>2</v>
-      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Vita Coco - Coconut Water 1L</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Vita Coco - Coconut Water 500ml</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Wrap - EZ Poly (8" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Wrap - Foil (9" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>Wrap - Paper (6" x 10.75")</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="n">
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="n">
         <v>1</v>
       </c>
     </row>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Acai Powder</t>
+          <t>Bag - Wax (Sandwich)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -459,50 +459,50 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Apple Cider (Gal)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bag - Poly (Retail Portion)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Bindi - Cake Tiramisu Round</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bag - Wax (Sandwich)</t>
+          <t>Boston Coffee Cake - Apple Cinnamon</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>1</v>
@@ -511,7 +511,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bag Paper - Baguette</t>
+          <t>Box Cake - 8x8x5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -521,33 +521,33 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bindi - Cake Tiramisu Round</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Bragg - Ginger Lemon Honey</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Capers</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="n">
-        <v>2</v>
-      </c>
+          <t>Bragg - Honey &amp; Green Tea</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -558,9 +558,7 @@
           <t>Celsius - Vibe Peach, Tropical, Arctic</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>2</v>
       </c>
@@ -583,7 +581,9 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -605,47 +605,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Container - Deli (16oz)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Container - Deli (32oz)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Container - Soup (16oz)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Container - Deli (8oz)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+          <t>Container - Soup (8oz)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -653,49 +653,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Container - Muffin (1 Pack)</t>
+          <t>Copy Paper (8.5" x 11")</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Container - Plastic Clamshell (6")</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2</v>
-      </c>
+          <t>Cup - Espresso (4oz)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Container - Soup (16oz)</t>
+          <t>Cup - Hot (8oz)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
@@ -703,7 +701,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Container - Soup (32oz)</t>
+          <t>Cup - Portion (2oz)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -712,112 +710,96 @@
         <v>1</v>
       </c>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Container - Soup (8oz)</t>
+          <t>Cup - Portion (3.25oz)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cup - Espresso (4oz)</t>
+          <t>DV - Cheddar Lovers Snack Mix (bulk)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cup - Hot (8oz)</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>4</v>
-      </c>
+          <t>DV - Chewey Caramel w/Pretzel (Sweet Jubilee)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cup - Portion (3.25oz)</t>
+          <t>DV - Chocolate Mini Pretzel</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Degreaser - for Panini Press (Dawn)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - Chocolate Sticks (bulk)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egg Patty - Vegan</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - Dk Choc Rasp Cup (bulk)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Eggs (In-Shell)</t>
+          <t>DV - Gummi Bears (8 oz)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -825,36 +807,32 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Employee Water</t>
+          <t>DV - Gummi Peach Rings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4</v>
-      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
+          <t>DV - Gummi Sharks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
@@ -863,67 +841,63 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
+          <t>DV - Lots O Licorice</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Mango</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - Milk Caramel Peanut Cluster (bulk)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
+          <t>DV - Milk Choc Pretzel w/Toffee (bulk)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Flax Seeds</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - PB filled Pretzels (bulk)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Apple</t>
+          <t>DV - Real Fruit Sour Bursts (bulk)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -931,41 +905,41 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Blueberry</t>
+          <t>DV - Salted Caramel Snk Mix (bulk)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Chip</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - Sour Neon Gummi Worms</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
+          <t>DV - Wasabi Peas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -973,121 +947,125 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Mixed Berry</t>
+          <t>Employee Water</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="n">
-        <v>1</v>
-      </c>
+      <c r="C37" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Hazelnut Coffee (Grounded, Bulk)</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2</v>
-      </c>
+          <t>Essentia Water</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
         <v>1</v>
       </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Honey - Jug</t>
+          <t>Evian 1L</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ice Melt</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>FRZ Fruit - Mango</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Iced Tea - Black</t>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Ginger Beer</t>
+          <t>Fiji Water 1L</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ithaca Soda - Root Beer</t>
+          <t>Fiji Water 500ml</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>1</v>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>1</v>
       </c>
@@ -1097,21 +1075,21 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jacquet - Belgian Waffles</t>
+          <t>Grandma's Coffee Cake - Apple</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>1</v>
-      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jam - Strawberry (Retail)</t>
+          <t>Grandma's Coffee Cake - Banana Walnut</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1125,21 +1103,21 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Box (160oz)</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
+          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1153,64 +1131,54 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Joe Tea - Black Cherry</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kilogram Chai Concentrate</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>2</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1</v>
-      </c>
-      <c r="D49" t="n">
-        <v>2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>6</v>
-      </c>
+          <t>Grandma's Coffee Cake - Cranberry</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lid - Deli (6/32oz)</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2</v>
-      </c>
+          <t>Grandma's Coffee Cake - Mixed Berry</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="n">
-        <v>2</v>
-      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lid - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>Hazelnut Coffee (Grounded, Bulk)</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>1</v>
@@ -1221,13 +1189,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Lid - Portion (3.25oz)</t>
+          <t>Honey - Jug</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>1</v>
-      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>2</v>
       </c>
@@ -1237,110 +1203,100 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lid - Soup (32oz)</t>
+          <t>Hot Chocolate (Bulk)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3</v>
-      </c>
-      <c r="C54" t="n">
-        <v>1</v>
-      </c>
+          <t>Ice Melt</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>4</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lid Espresso - 4oz</t>
+          <t>Iced Tea - Black</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Maple Syrup (pure)</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>2</v>
-      </c>
+          <t>Iced Tea - Green Citrus Ginko</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="n">
-        <v>2</v>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Matcha - Jade Leaf</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3</v>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
+          <t>Jacquet - Belgian Waffles</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Monin - Butter Pecan</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="n">
-        <v>1</v>
-      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Monin - Cinnamon</t>
+          <t>Joe Tea - Black Cherry</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
@@ -1349,7 +1305,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Mop Head Cut (White)</t>
+          <t>Joe Tea - Classic Lemonade</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1363,72 +1319,82 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mustard - Honey</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+          <t>Kilogram Chai Concentrate</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2</v>
+      </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oats</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+          <t>Lid - Deli (6/32oz)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="n">
-        <v>1</v>
-      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2</v>
-      </c>
+          <t>Lid - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>1</v>
       </c>
-      <c r="D63" t="n">
-        <v>2</v>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Plate - Paper (7")</t>
+          <t>Lid - Portion (3.25oz)</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Lid - Soup (32oz)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
         <v>1</v>
@@ -1437,177 +1403,179 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Red Bull - Amber</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>Lid - Soup (6/16 oz)</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>4</v>
+      </c>
       <c r="C66" t="n">
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Register Tape - Paper (3" x 165')</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid Espresso - 4oz</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
+          <t>Maple Syrup (pure)</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 12oz</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>Matcha</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3</v>
+      </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="n">
+        <v>2</v>
+      </c>
       <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>Monin - Butter Pecan</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="n">
-        <v>2</v>
-      </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>5</v>
-      </c>
-      <c r="C71" t="n">
-        <v>1</v>
-      </c>
-      <c r="D71" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+          <t>Monin - Cinnamon</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
       <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sugar - Extra Fine</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>Mop Head Cut (White)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2</v>
+      </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="n">
-        <v>1</v>
-      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sugar - Light Brown</t>
+          <t>Natures Bakery - Fig w/ Apple Cinnamon</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="n">
-        <v>1</v>
-      </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Supplement - Antioxident</t>
+          <t>Natures Bakery - Fig w/ Blueberry</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Supplement - Collagen</t>
+          <t>Oil - Olive Extra Virgin</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="n">
-        <v>1</v>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Supplement - Whey Protein</t>
+          <t>Panini Sheets - 16x8 3/8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="n">
-        <v>1</v>
-      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
+          <t>Peanut Butter - Chunky</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1623,11 +1591,13 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sweet Street - Pie Caramel Apple Granny Sliced</t>
+          <t>Peanut Butter - Creamy</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
@@ -1637,137 +1607,119 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sweet Street - Pie Oreo Cookie Bash Sliced</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>6</v>
-      </c>
+          <t>Red Bull - Amber</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="n">
-        <v>6</v>
-      </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>8</v>
-      </c>
+          <t>Register Tape - Paper (3" x 165')</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="n">
-        <v>6</v>
-      </c>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
       <c r="C82" t="n">
         <v>1</v>
       </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="n">
-        <v>1</v>
-      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>6</v>
-      </c>
+          <t>Saratoga Sparkling 12oz</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="n">
-        <v>2</v>
-      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tissues/Kleenex</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
+          <t>Saratoga Sparkling 28oz</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="n">
-        <v>2</v>
-      </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="n">
-        <v>2</v>
-      </c>
-      <c r="E85" t="n">
-        <v>2</v>
-      </c>
-      <c r="F85" t="n">
-        <v>1</v>
-      </c>
+          <t>Scrubbies - Steel</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Smoked Salmon (Retail Pack)</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4</v>
-      </c>
-      <c r="C86" t="n">
-        <v>3</v>
-      </c>
-      <c r="D86" t="n">
-        <v>4</v>
-      </c>
-      <c r="E86" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="n">
         <v>1</v>
       </c>
@@ -1775,89 +1727,85 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Torani - Pumpkin Pie Sauce</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
+          <t>Smoked Salmon (Sliced)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="n">
-        <v>1</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Supplement - Antioxident</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>1</v>
+      </c>
       <c r="E88" t="n">
-        <v>2</v>
-      </c>
-      <c r="F88" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Urnex - Cafiza</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="n">
-        <v>1</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="n">
-        <v>2</v>
-      </c>
+          <t>Supplement - Collagen</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Urnex - Rinza</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="n">
-        <v>2</v>
-      </c>
+          <t>Supplement - Whey Protein</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2</v>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 1L</t>
+          <t>Sweet Street - Bar Lemon Luscious Sliced</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="n">
-        <v>1</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
+          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -1865,9 +1813,7 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
         <v>1</v>
       </c>
@@ -1875,33 +1821,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Wrap - EZ Poly (8" x 10.75")</t>
+          <t>Sweet Street - Chocolate Lovin</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="n">
-        <v>1</v>
-      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="n">
-        <v>3</v>
-      </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
+          <t>Sweet Street - Pie Choc PB Cup Sliced</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
-      </c>
-      <c r="C94" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
@@ -1909,42 +1851,266 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2</v>
-      </c>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Wrap - Paper (6" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tea Bags - Lemon Ginger (Twinings)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Torani - Caramel Sauce</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Torani - Dark Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>6</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Urnex - Rinza</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Vita Coco - Coconut Water 500ml</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Vita Coco - Pineapple</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>White Hot Chocolate - Ghirardelli</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Wrap - EZ Poly (8" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Wrap - Foil (9" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Wrap - Paper (6" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/combined_orders_Ithaca Bakery.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bag - Wax (Sandwich)</t>
+          <t>Apple Cider (Gal)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -459,66 +459,64 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bag Paper - Baguette</t>
+          <t>Bag - Wax (Sandwich)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bindi - Cake Tiramisu Round</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
+          <t>Bag Paper - Baguette</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boston Coffee Cake - Apple Cinnamon</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Bindi - Cake Tiramisu Round</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Box Cake - 8x8x5</t>
+          <t>Boston Coffee Cake - Apple Cinnamon</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>1</v>
@@ -527,21 +525,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bragg - Ginger Lemon Honey</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
+          <t>Box Cake - 8x8x5</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bragg - Honey &amp; Green Tea</t>
+          <t>Bragg - Ginger Lemon Honey</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -555,46 +555,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
+          <t>Bragg - Honey &amp; Green Tea</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Chobani - Drinkables (Assorted Case)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
+          <t>Celsius - Vibe Peach, Tropical, Arctic</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coffee Stirrer (Bamboo)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Chobani - Drinkables (Assorted Case)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
@@ -605,29 +605,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Container - Deli (32oz)</t>
+          <t>Coffee Stirrer (Bamboo)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Container - Soup (16oz)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>5</v>
-      </c>
+          <t>Container - Deli (32oz)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -635,17 +633,15 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Container - Soup (8oz)</t>
+          <t>Container - Soup (16oz)</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="n">
         <v>4</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -653,13 +649,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Copy Paper (8.5" x 11")</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+          <t>Container - Soup (8oz)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
@@ -667,47 +667,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cup - Espresso (4oz)</t>
+          <t>Copy Paper (8.5" x 11")</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cup - Hot (8oz)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4</v>
-      </c>
+          <t>Cup - Espresso (4oz)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
       <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cup - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+          <t>Cup - Hot (8oz)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
@@ -715,35 +715,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cup - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2</v>
-      </c>
+          <t>Cup - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>DV - Cheddar Lovers Snack Mix (bulk)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Cup - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>6</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DV - Chewey Caramel w/Pretzel (Sweet Jubilee)</t>
+          <t>DV - Cheddar Lovers Snack Mix (bulk)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -757,7 +757,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DV - Chocolate Mini Pretzel</t>
+          <t>DV - Chewey Caramel w/Pretzel (Sweet Jubilee)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -771,7 +771,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DV - Chocolate Sticks (bulk)</t>
+          <t>DV - Chocolate Mini Pretzel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -779,13 +779,13 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DV - Dk Choc Rasp Cup (bulk)</t>
+          <t>DV - Chocolate Sticks (bulk)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -793,13 +793,13 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DV - Gummi Bears (8 oz)</t>
+          <t>DV - Dk Choc Rasp Cup (bulk)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -813,7 +813,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DV - Gummi Peach Rings</t>
+          <t>DV - Gummi Bears (8 oz)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -821,41 +821,41 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DV - Gummi Sharks</t>
+          <t>DV - Gummi Peach Rings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>6</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DV - Lots O Licorice</t>
+          <t>DV - Gummi Sharks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>6</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>DV - Milk Caramel Peanut Cluster (bulk)</t>
+          <t>DV - Lots O Licorice</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -869,7 +869,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DV - Milk Choc Pretzel w/Toffee (bulk)</t>
+          <t>DV - Milk Caramel Peanut Cluster (bulk)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DV - PB filled Pretzels (bulk)</t>
+          <t>DV - Milk Choc Pretzel w/Toffee (bulk)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -897,7 +897,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DV - Real Fruit Sour Bursts (bulk)</t>
+          <t>DV - PB filled Pretzels (bulk)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -911,7 +911,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DV - Salted Caramel Snk Mix (bulk)</t>
+          <t>DV - Real Fruit Sour Bursts (bulk)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -925,7 +925,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DV - Sour Neon Gummi Worms</t>
+          <t>DV - Salted Caramel Snk Mix (bulk)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -933,13 +933,13 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DV - Wasabi Peas</t>
+          <t>DV - Sour Neon Gummi Worms</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -947,57 +947,59 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Degreaser - for Panini Press (Dawn)</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
+          <t>DV - Wasabi Peas</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Employee Water</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Degreaser - for Panini Press (Dawn)</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>2</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Essentia Water</t>
+          <t>Employee Water</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Evian 1L</t>
+          <t>Essentia Water</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1011,99 +1013,99 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Mango</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="n">
-        <v>1</v>
-      </c>
+          <t>Evian 1L</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FRZ Fruit - Raspberry (Whole)</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>FRZ Fruit - Mango</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Fiji Water 1L</t>
+          <t>FRZ Fruit - Raspberry (Whole)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fiji Water 500ml</t>
+          <t>Fiji Water 1L</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Apple</t>
+          <t>Fiji Water 500ml</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Banana Walnut</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
+          <t>Grandma's Coffee Cake - Apple</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+          <t>Grandma's Coffee Cake - Banana Walnut</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1117,68 +1119,66 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>Grandma's Coffee Cake - Chocolate Chip</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cinnamon</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
+          <t>Grandma's Coffee Cake - Chocolate Walnut</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Cranberry</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>Grandma's Coffee Cake - Cinnamon</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grandma's Coffee Cake - Mixed Berry</t>
+          <t>Grandma's Coffee Cake - Cranberry</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hazelnut Coffee (Grounded, Bulk)</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>3</v>
-      </c>
+          <t>Grandma's Coffee Cake - Mixed Berry</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>1</v>
@@ -1189,13 +1189,15 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Honey - Jug</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Hazelnut Coffee (Grounded, Bulk)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3</v>
+      </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
@@ -1203,15 +1205,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Hot Chocolate (Bulk)</t>
+          <t>Honey - Jug</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
-        <v>1</v>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
@@ -1219,11 +1219,13 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ice Melt</t>
+          <t>Hot Chocolate (Bulk)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
       <c r="D54" t="n">
         <v>1</v>
       </c>
@@ -1233,7 +1235,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Iced Tea - Black</t>
+          <t>Ice Melt</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1247,7 +1249,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iced Tea - Green Citrus Ginko</t>
+          <t>Iced Tea - Black</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1261,189 +1263,185 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jacquet - Belgian Waffles</t>
+          <t>Iced Tea - Green Citrus Ginko</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="n">
-        <v>1</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Box (96oz)</t>
+          <t>Jacquet - Belgian Waffles</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Joe Tea - Black Cherry</t>
+          <t>Java Box (96oz)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Joe Tea - Classic Lemonade</t>
+          <t>Joe Tea - Black Cherry</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
       <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Kilogram Chai Concentrate</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2</v>
-      </c>
+          <t>Joe Tea - Classic Lemonade</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>1</v>
       </c>
-      <c r="D61" t="n">
-        <v>2</v>
-      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="n">
-        <v>1</v>
-      </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lid - Deli (6/32oz)</t>
+          <t>Kilogram Chai Concentrate</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
       </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="n">
-        <v>3</v>
-      </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Lid - Portion (2oz)</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Lid - Deli (6/32oz)</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>6</v>
+      </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
       <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lid - Portion (3.25oz)</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>2</v>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Lid - Soup (32oz)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>Lid - Portion (3.25oz)</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2</v>
+      </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
         <v>1</v>
       </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
-        <v>1</v>
-      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lid - Soup (6/16 oz)</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>4</v>
-      </c>
-      <c r="C66" t="n">
-        <v>1</v>
-      </c>
+          <t>Lid - Soup (32oz)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lid Espresso - 4oz</t>
+          <t>Lid - Soup (6/16 oz)</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="n">
-        <v>2</v>
-      </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maple Syrup (pure)</t>
+          <t>Lid Espresso - 4oz</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
@@ -1451,79 +1449,83 @@
         <v>2</v>
       </c>
       <c r="F68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>Maple Syrup (pure)</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="n">
         <v>2</v>
       </c>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Monin - Butter Pecan</t>
+          <t>Matcha</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="n">
+        <v>2</v>
+      </c>
       <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Monin - Cinnamon</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>Monin - Butter Pecan</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2</v>
+      </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mop Head Cut (White)</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>2</v>
-      </c>
+          <t>Monin - Cinnamon</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="n">
-        <v>2</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
       <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Natures Bakery - Fig w/ Apple Cinnamon</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>Mop Head Cut (White)</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>2</v>
+      </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
@@ -1531,7 +1533,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Natures Bakery - Fig w/ Blueberry</t>
+          <t>Natures Bakery - Fig w/ Apple Cinnamon</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1540,90 +1542,88 @@
         <v>1</v>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="n">
-        <v>4</v>
-      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Oil - Olive Extra Virgin</t>
+          <t>Natures Bakery - Fig w/ Blueberry</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="n">
-        <v>1</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Panini Sheets - 16x8 3/8</t>
+          <t>Oil - Olive Extra Virgin</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr"/>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
-      <c r="F76" t="n">
-        <v>2</v>
-      </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Peanut Butter - Chunky</t>
+          <t>Panini Sheets - 16x8 3/8</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" t="n">
-        <v>1</v>
-      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Peanut Butter - Creamy</t>
+          <t>Peanut Butter - Chunky</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="n">
-        <v>2</v>
-      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Red Bull</t>
+          <t>Peanut Butter - Creamy</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
-        <v>1</v>
-      </c>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Red Bull - Amber</t>
+          <t>Red Bull</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -1632,12 +1632,14 @@
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Register Tape - Paper (3" x 165')</t>
+          <t>Red Bull - Amber</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -1651,31 +1653,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Register Tape - Thermal (3.125" x 230')</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
+          <t>Register Tape - Paper (3" x 165')</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
         <v>1</v>
       </c>
-      <c r="D82" t="n">
-        <v>1</v>
-      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 12oz</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+          <t>Register Tape - Thermal (3.125" x 230')</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
@@ -1683,27 +1685,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Saratoga Sparkling 28oz</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
+          <t>Saratoga Sparkling 12oz</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Scrubbies - Steel</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="n">
-        <v>1</v>
-      </c>
+          <t>Saratoga Sparkling 28oz</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
@@ -1711,57 +1713,55 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Retail Pack)</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>Scrubbies - Steel</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="n">
-        <v>1</v>
-      </c>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Smoked Salmon (Sliced)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="n">
-        <v>2</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3</v>
-      </c>
+          <t>Smoked Salmon (Retail Pack)</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Supplement - Antioxident</t>
+          <t>Smoked Salmon (Sliced)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
       <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="n">
-        <v>1</v>
-      </c>
-      <c r="F88" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Supplement - Collagen</t>
+          <t>Supplement - Antioxident</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -1769,18 +1769,18 @@
       <c r="D89" t="n">
         <v>1</v>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
       <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Supplement - Whey Protein</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2</v>
-      </c>
+          <t>Supplement - Collagen</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
         <v>1</v>
@@ -1791,10 +1791,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sweet Street - Bar Lemon Luscious Sliced</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>Supplement - Whey Protein</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
         <v>1</v>
@@ -1805,7 +1807,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
+          <t>Sweet Street - Bar Lemon Luscious Sliced</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -1814,19 +1816,19 @@
         <v>1</v>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sweet Street - Chocolate Lovin</t>
+          <t>Sweet Street - Cheesecake Rasp White Choc Brulee Sliced</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>1</v>
+      </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="n">
         <v>1</v>
@@ -1835,209 +1837,209 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sweet Street - Pie Choc PB Cup Sliced</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
+          <t>Sweet Street - Chocolate Lovin</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="n">
-        <v>2</v>
-      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey (Twinings)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
-      <c r="C95" t="n">
-        <v>1</v>
-      </c>
+          <t>Sweet Street - Pie Choc PB Cup Sliced</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
         <v>2</v>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="n">
-        <v>4</v>
-      </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+          <t>Tea Bags - Earl Grey (Twinings)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tea Bags - English Breakfast (Twinings)</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>2</v>
-      </c>
-      <c r="C97" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - Earl Grey Lavender (Twinings)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>2</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2</v>
-      </c>
-      <c r="F97" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tea Bags - Lemon Ginger (Twinings)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
+          <t>Tea Bags - English Breakfast (Twinings)</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
       <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2</v>
+      </c>
       <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
+          <t>Tea Bags - Lemon Ginger (Twinings)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="n">
-        <v>1</v>
-      </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Torani - Caramel Sauce</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>4</v>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="n">
-        <v>1</v>
-      </c>
+          <t>Tea Bags - Throat Coat (Traditional Medicinals)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="n">
         <v>1</v>
       </c>
-      <c r="F100" t="n">
-        <v>1</v>
-      </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Torani - Dark Chocolate Sauce</t>
+          <t>Torani - Caramel Sauce</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Torani - White Chocolate Sauce</t>
+          <t>Torani - Dark Chocolate Sauce</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
-      </c>
-      <c r="C102" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
       <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2</v>
+      </c>
       <c r="F102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Urnex - Rinza</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="n">
-        <v>1</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Torani - White Chocolate Sauce</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>1</v>
+      </c>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Vita Coco - Coconut Water 500ml</t>
+          <t>Urnex - Rinza</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="n">
-        <v>1</v>
-      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Vita Coco - Pineapple</t>
+          <t>Vita Coco - Coconut Water 500ml</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="n">
-        <v>1</v>
-      </c>
+      <c r="E105" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>White Hot Chocolate - Ghirardelli</t>
+          <t>Vita Coco - Pineapple</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -2051,21 +2053,21 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Wrap - EZ Poly (8" x 10.75")</t>
+          <t>White Hot Chocolate - Ghirardelli</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="n">
-        <v>1</v>
-      </c>
+      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Wrap - Foil (9" x 10.75")</t>
+          <t>Wrap - EZ Poly (8" x 10.75")</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2079,38 +2081,52 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Wrap - Paper (15" x 10.75")</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>2</v>
-      </c>
+          <t>Wrap - Foil (9" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>1</v>
       </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="n">
-        <v>1</v>
-      </c>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>Wrap - Paper (15" x 10.75")</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>Wrap - Paper (6" x 10.75")</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
